--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484337_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484337_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.215</v>
+        <v>12.3244</v>
       </c>
       <c r="E2" t="n">
-        <v>12.5672</v>
+        <v>11.7582</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6479</v>
+        <v>0.5662</v>
       </c>
       <c r="G2" t="n">
         <v>9.527100000000001</v>
@@ -610,13 +610,13 @@
         <v>0.7814</v>
       </c>
       <c r="S2" t="n">
-        <v>2.02</v>
+        <v>1.1294</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9096</v>
+        <v>1.1007</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1104</v>
+        <v>0.0287</v>
       </c>
       <c r="V2" t="n">
         <v>0.8865</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4106</v>
+        <v>6.2084</v>
       </c>
       <c r="E3" t="n">
-        <v>6.007</v>
+        <v>2.2261</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4036</v>
+        <v>3.9823</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8797</v>
+        <v>3.7082</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5155</v>
+        <v>3.1274</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3642</v>
+        <v>0.5807</v>
       </c>
       <c r="J3" t="n">
-        <v>2.039</v>
+        <v>1.4357</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9442</v>
+        <v>2.0683</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09470000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1593</v>
+        <v>2.2725</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4287</v>
+        <v>1.0591</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2694</v>
+        <v>1.2134</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1953</v>
+        <v>2.1488</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2304</v>
+        <v>0.3514</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8396</v>
+        <v>0.7905</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6092</v>
+        <v>-0.439</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1751</v>
+        <v>5.2889</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5411</v>
+        <v>3.3264</v>
       </c>
       <c r="F4" t="n">
-        <v>4.634</v>
+        <v>1.9625</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6388</v>
+        <v>4.079</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9394</v>
+        <v>2.1909</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6994</v>
+        <v>1.8881</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4355</v>
+        <v>3.415</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0054</v>
+        <v>1.3917</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4301</v>
+        <v>2.0233</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2033</v>
+        <v>0.664</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.7992</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2692</v>
+        <v>-0.1352</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.1255</v>
+        <v>1.1721</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.8836</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5018</v>
+        <v>0.37</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5519</v>
+        <v>0.2436</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9499</v>
+        <v>0.1265</v>
       </c>
       <c r="V4" t="n">
-        <v>2.16</v>
+        <v>-0.3321</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4373</v>
+        <v>-0.3321</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.2494</v>
+        <v>4.9506</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4578</v>
+        <v>4.2475</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7916</v>
+        <v>0.7032</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7082</v>
+        <v>1.8797</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1274</v>
+        <v>1.5155</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5807</v>
+        <v>0.3642</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4357</v>
+        <v>2.039</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0683</v>
+        <v>1.9442</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6326000000000001</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>2.2725</v>
+        <v>-0.1593</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0591</v>
+        <v>-0.4287</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2134</v>
+        <v>0.2694</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1488</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1488</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6075</v>
+        <v>0.7704</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0221</v>
+        <v>1.08</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6296</v>
+        <v>-0.3096</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.3554</v>
+        <v>4.8935</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7197</v>
+        <v>0.9949</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6357</v>
+        <v>3.8986</v>
       </c>
       <c r="G6" t="n">
-        <v>4.079</v>
+        <v>3.6388</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1909</v>
+        <v>1.9394</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8881</v>
+        <v>1.6994</v>
       </c>
       <c r="J6" t="n">
-        <v>3.415</v>
+        <v>2.4355</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3917</v>
+        <v>1.0054</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0233</v>
+        <v>1.4301</v>
       </c>
       <c r="M6" t="n">
-        <v>0.664</v>
+        <v>1.2033</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7992</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1352</v>
+        <v>0.2692</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1721</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.8836</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5635</v>
+        <v>2.2202</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3631</v>
+        <v>1.0057</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2004</v>
+        <v>1.2145</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3321</v>
+        <v>2.16</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3321</v>
+        <v>2.4373</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.3038</v>
+        <v>4.3444</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2252</v>
+        <v>0.9936</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0785</v>
+        <v>3.3509</v>
       </c>
       <c r="G7" t="n">
         <v>3.0479</v>
@@ -1000,13 +1000,13 @@
         <v>2.1488</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0605</v>
+        <v>1.1012</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2642</v>
+        <v>1.0325</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2037</v>
+        <v>0.0687</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.9478</v>
+        <v>2.9206</v>
       </c>
       <c r="E8" t="n">
         <v>1.0805</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8673</v>
+        <v>1.8401</v>
       </c>
       <c r="G8" t="n">
         <v>1.0868</v>
@@ -1078,13 +1078,13 @@
         <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6889</v>
+        <v>0.6617</v>
       </c>
       <c r="T8" t="n">
         <v>0.2504</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4385</v>
+        <v>0.4112</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9911</v>
+        <v>1.6489</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3663</v>
+        <v>1.8608</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3753</v>
+        <v>-0.2119</v>
       </c>
       <c r="G9" t="n">
         <v>1.1942</v>
@@ -1156,13 +1156,13 @@
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2108</v>
+        <v>-0.1314</v>
       </c>
       <c r="T9" t="n">
-        <v>0.743</v>
+        <v>0.2374</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5322</v>
+        <v>-0.3688</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5776</v>
+        <v>1.1359</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0521</v>
+        <v>-0.3849</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6297</v>
+        <v>1.5208</v>
       </c>
       <c r="G10" t="n">
         <v>1.0217</v>
@@ -1234,13 +1234,13 @@
         <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0301</v>
+        <v>-0.4719</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.652</v>
+        <v>0.0152</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3782</v>
+        <v>-0.4871</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0573</v>
+        <v>0.4423</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6472</v>
+        <v>-0.3438</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7044</v>
+        <v>0.7861</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5913</v>
@@ -1312,13 +1312,13 @@
         <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2031</v>
+        <v>0.5881</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2504</v>
+        <v>0.5538</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0474</v>
+        <v>0.0343</v>
       </c>
       <c r="V11" t="n">
         <v>0.6642</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7661</v>
+        <v>-0.4355</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8259</v>
+        <v>-0.5226</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0598</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1239</v>
@@ -1390,13 +1390,13 @@
         <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5299</v>
+        <v>0.8605</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0083</v>
+        <v>0.3117</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5215</v>
+        <v>0.5488</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8003</v>
+        <v>-3.7033</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.738</v>
+        <v>-3.2324</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0623</v>
+        <v>-0.4709</v>
       </c>
       <c r="G13" t="n">
         <v>-5.1896</v>
@@ -1468,13 +1468,13 @@
         <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8033</v>
+        <v>0.9003</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0689</v>
+        <v>0.5744</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.3259</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>39.71669999999999</v>
+        <v>40.01910000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>21.7016</v>
+        <v>22.00429999999999</v>
       </c>
       <c r="F14" t="n">
         <v>18.0149</v>
@@ -1525,7 +1525,7 @@
         <v>12.401</v>
       </c>
       <c r="L14" t="n">
-        <v>4.730499999999997</v>
+        <v>4.730500000000001</v>
       </c>
       <c r="M14" t="n">
         <v>5.1471</v>
@@ -1546,13 +1546,13 @@
         <v>14.6509</v>
       </c>
       <c r="S14" t="n">
-        <v>8.047600000000001</v>
+        <v>8.3499</v>
       </c>
       <c r="T14" t="n">
-        <v>6.8933</v>
+        <v>7.1959</v>
       </c>
       <c r="U14" t="n">
-        <v>1.154</v>
+        <v>1.1541</v>
       </c>
       <c r="V14" t="n">
         <v>5.4838</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3846</v>
+        <v>0.9899</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2132</v>
+        <v>0.3935</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5978</v>
+        <v>0.5965</v>
       </c>
       <c r="G15" t="n">
         <v>0.5580000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>0.586</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7595</v>
+        <v>-0.1541</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5915</v>
+        <v>0.0152</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.168</v>
+        <v>-0.1694</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3794</v>
+        <v>0.3444</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1539</v>
+        <v>2.255</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7745</v>
+        <v>-1.9106</v>
       </c>
       <c r="G16" t="n">
         <v>1.0876</v>
@@ -1702,13 +1702,13 @@
         <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8254</v>
+        <v>-0.8605</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4621</v>
+        <v>-0.3609</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3633</v>
+        <v>-0.4995</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6642</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3653</v>
+        <v>-1.2175</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0312</v>
+        <v>-0.829</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3341</v>
+        <v>-0.3886</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1156</v>
@@ -1780,13 +1780,13 @@
         <v>0.3907</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6637</v>
+        <v>-0.5159</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4237</v>
+        <v>-0.2214</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.24</v>
+        <v>-0.2945</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>P. BORT DOMINGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5204</v>
+        <v>-1.7311</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4587</v>
+        <v>0.311</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9791</v>
+        <v>-2.0421</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0942</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8642</v>
+        <v>0.65</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.23</v>
+        <v>-0.0951</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0046</v>
+        <v>1.1047</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0359</v>
+        <v>1.0642</v>
       </c>
       <c r="L18" t="n">
         <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0988</v>
+        <v>-0.5498</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8283</v>
+        <v>-0.4142</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2704</v>
+        <v>-0.1356</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5738</v>
+        <v>-0.2628</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4308</v>
+        <v>0.183</v>
       </c>
       <c r="U18" t="n">
-        <v>0.143</v>
+        <v>-0.4458</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2186</v>
+        <v>-1.8279</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. BORT DOMINGUEZ</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6637</v>
+        <v>-2.6677</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5132</v>
+        <v>-0.5524</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.177</v>
+        <v>-2.1153</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5548999999999999</v>
+        <v>-1.0942</v>
       </c>
       <c r="H19" t="n">
-        <v>0.65</v>
+        <v>-0.8642</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0951</v>
+        <v>-0.23</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1047</v>
+        <v>0.0046</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0642</v>
+        <v>-0.0359</v>
       </c>
       <c r="L19" t="n">
         <v>0.0405</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5498</v>
+        <v>-1.0988</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4142</v>
+        <v>-0.8283</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1356</v>
+        <v>-0.2704</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1953</v>
+        <v>0.4265</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3853</v>
+        <v>0.4197</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5806</v>
+        <v>0.0068</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8279</v>
+        <v>-1.2186</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8279</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>J. PINEÑO JIMENEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0524</v>
+        <v>-3.0328</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3787</v>
+        <v>-2.0384</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6737</v>
+        <v>-0.9944</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2764</v>
+        <v>-1.6406</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3881</v>
+        <v>-0.8716</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8883</v>
+        <v>-0.769</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.8381</v>
+        <v>-0.6119</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4899</v>
+        <v>0.0217</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3482</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4382</v>
+        <v>-1.0287</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8982</v>
+        <v>-0.8933</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5401</v>
+        <v>-0.1354</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4193</v>
+        <v>-1.3921</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2175</v>
+        <v>-0.4497</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2018</v>
+        <v>-0.9424</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PINEÑO JIMENEZ</t>
+          <t>P. DIAZ KAUFFMANN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3167</v>
+        <v>-3.1242</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2406</v>
+        <v>0.0429</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0761</v>
+        <v>-3.1671</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6406</v>
+        <v>-0.2223</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8716</v>
+        <v>-0.3564</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.769</v>
+        <v>0.134</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6119</v>
+        <v>1.2906</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0217</v>
+        <v>1.2906</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0287</v>
+        <v>-1.5129</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8933</v>
+        <v>-1.647</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1354</v>
+        <v>0.134</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6761</v>
+        <v>-1.2339</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.652</v>
+        <v>0.0964</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0241</v>
+        <v>-1.3304</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. DIAZ KAUFFMANN</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3952</v>
+        <v>-3.352</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0429</v>
+        <v>-1.3787</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4381</v>
+        <v>-1.9733</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2223</v>
+        <v>-3.2764</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3564</v>
+        <v>-1.3881</v>
       </c>
       <c r="I22" t="n">
-        <v>0.134</v>
+        <v>-1.8883</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2906</v>
+        <v>-1.8381</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2906</v>
+        <v>-0.4899</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.3482</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5129</v>
+        <v>-1.4382</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.647</v>
+        <v>-0.8982</v>
       </c>
       <c r="O22" t="n">
-        <v>0.134</v>
+        <v>-0.5401</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5049</v>
+        <v>0.1197</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0964</v>
+        <v>0.2175</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.6014</v>
+        <v>-0.0978</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8427</v>
+        <v>-5.1449</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5402</v>
+        <v>-2.779</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3025</v>
+        <v>-2.3659</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.917</v>
+        <v>-3.437</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6219</v>
+        <v>-3.0454</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2951</v>
+        <v>-0.3916</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.4784</v>
+        <v>-0.2356</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.8586</v>
+        <v>-1.4634</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6198</v>
+        <v>1.2278</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4386</v>
+        <v>-3.2014</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7634</v>
+        <v>-1.582</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6753</v>
+        <v>-1.6194</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
         <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9024</v>
+        <v>-1.2587</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0851</v>
+        <v>-0.59</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8173</v>
+        <v>-0.6687</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2186</v>
+        <v>0.3321</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.0785</v>
+        <v>-5.9101</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3857</v>
+        <v>-3.7425</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6928</v>
+        <v>-2.1677</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.437</v>
+        <v>-3.917</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.0454</v>
+        <v>-2.6219</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3916</v>
+        <v>-1.2951</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2356</v>
+        <v>-2.4784</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4634</v>
+        <v>-1.8586</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2278</v>
+        <v>-0.6198</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.2014</v>
+        <v>-1.4386</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.582</v>
+        <v>-0.7634</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6194</v>
+        <v>-0.6753</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
         <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.1922</v>
+        <v>-0.9698</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1967</v>
+        <v>-0.2874</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9955000000000001</v>
+        <v>-0.6824</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3321</v>
+        <v>-1.2186</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3321</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. BERMEJO JARAMILLO</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.0762</v>
+        <v>-6.7495</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.5403</v>
+        <v>-4.6516</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5359</v>
+        <v>-2.0978</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.3772</v>
+        <v>-5.3987</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.8389</v>
+        <v>-2.8494</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.5383</v>
+        <v>-2.5493</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.9199</v>
+        <v>-2.272</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.3267</v>
+        <v>-1.6117</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6603</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.4573</v>
+        <v>-3.1267</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.5121</v>
+        <v>-1.2377</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-1.8891</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.3907</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7538</v>
+        <v>-0.1471</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3331</v>
+        <v>-0.004</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0869</v>
+        <v>-0.1432</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.5545</v>
+        <v>0.5545</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>P. BERMEJO JARAMILLO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.1696</v>
+        <v>-7.4469</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.8539</v>
+        <v>-5.0458</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.3157</v>
+        <v>-2.4011</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.3987</v>
+        <v>-5.3772</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.8494</v>
+        <v>-3.8389</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.5493</v>
+        <v>-1.5383</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.272</v>
+        <v>-2.9199</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.6117</v>
+        <v>-2.3267</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.6603</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.1267</v>
+        <v>-2.4573</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.2377</v>
+        <v>-1.5121</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.8891</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.7581</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5672</v>
+        <v>-1.1246</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2062</v>
+        <v>-0.1725</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3611</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>0.5545</v>
+        <v>-0.5545</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-39.7167</v>
+        <v>-39.0424</v>
       </c>
       <c r="E27" t="n">
-        <v>-18.0151</v>
+        <v>-18.015</v>
       </c>
       <c r="F27" t="n">
-        <v>-21.7017</v>
+        <v>-21.0274</v>
       </c>
       <c r="G27" t="n">
         <v>-22.2785</v>
@@ -2536,7 +2536,7 @@
         <v>-5.1471</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.453800000000001</v>
+        <v>-2.4538</v>
       </c>
       <c r="L27" t="n">
         <v>-2.6934</v>
@@ -2551,7 +2551,7 @@
         <v>-4.7306</v>
       </c>
       <c r="P27" t="n">
-        <v>-3.906899999999999</v>
+        <v>-3.9069</v>
       </c>
       <c r="Q27" t="n">
         <v>-14.6505</v>
@@ -2560,16 +2560,16 @@
         <v>10.744</v>
       </c>
       <c r="S27" t="n">
-        <v>-8.0474</v>
+        <v>-7.3733</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.1542</v>
+        <v>-1.1541</v>
       </c>
       <c r="U27" t="n">
-        <v>-6.8934</v>
+        <v>-6.2194</v>
       </c>
       <c r="V27" t="n">
-        <v>-5.4837</v>
+        <v>-5.483700000000001</v>
       </c>
       <c r="W27" t="n">
         <v>2.9369</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484337_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484337_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,11 +1213,16 @@
       <c r="X9" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1234,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1359</v>
+        <v>1.521</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3849</v>
+        <v>1.521</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5208</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0217</v>
+        <v>1.521</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0857</v>
+        <v>0.307</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1074</v>
+        <v>1.214</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5765</v>
+        <v>1.521</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1433</v>
+        <v>0.307</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4333</v>
+        <v>1.214</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4452</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2289</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6741</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4719</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0152</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4871</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1250,12 +1295,17 @@
       </c>
       <c r="X10" t="n">
         <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. BAYO GARCIA</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4423</v>
+        <v>1.1359</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3438</v>
+        <v>-0.3849</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7861</v>
+        <v>1.5208</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5913</v>
+        <v>1.0217</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4851</v>
+        <v>-0.0857</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0764</v>
+        <v>1.1074</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8976</v>
+        <v>0.5765</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0438</v>
+        <v>0.1433</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9414</v>
+        <v>0.4333</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6937</v>
+        <v>0.4452</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5587</v>
+        <v>-0.2289</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.135</v>
+        <v>0.6741</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5881</v>
+        <v>-0.4719</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5538</v>
+        <v>0.0152</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0343</v>
+        <v>-0.4871</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>G. BAYO GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4355</v>
+        <v>0.4423</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5226</v>
+        <v>-0.3438</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.7861</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1239</v>
+        <v>-1.5913</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0977</v>
+        <v>0.4851</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0263</v>
+        <v>-2.0764</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1192</v>
+        <v>-0.8976</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4707</v>
+        <v>1.0438</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6484</v>
+        <v>-1.9414</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2431</v>
+        <v>-0.6937</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5684</v>
+        <v>-0.5587</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6747</v>
+        <v>-0.135</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8605</v>
+        <v>0.5881</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3117</v>
+        <v>0.5538</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5488</v>
+        <v>0.0343</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7033</v>
+        <v>-1.9565</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2324</v>
+        <v>-2.0435</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4709</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.1896</v>
+        <v>-1.6449</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.8302</v>
+        <v>-0.4047</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.3594</v>
+        <v>-1.2402</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.0255</v>
+        <v>-0.4018</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.5314</v>
+        <v>0.1637</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.4941</v>
+        <v>-0.5655</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1641</v>
+        <v>-1.2431</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2988</v>
+        <v>-0.5684</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1346</v>
+        <v>-0.6747</v>
       </c>
       <c r="P13" t="n">
-        <v>0.586</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9003</v>
+        <v>0.8605</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5744</v>
+        <v>0.3117</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3259</v>
+        <v>0.5488</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,146 +1566,152 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>40.01910000000001</v>
+        <v>-3.7033</v>
       </c>
       <c r="E14" t="n">
-        <v>22.00429999999999</v>
+        <v>-3.2324</v>
       </c>
       <c r="F14" t="n">
-        <v>18.0149</v>
+        <v>-0.4709</v>
       </c>
       <c r="G14" t="n">
-        <v>22.2786</v>
+        <v>-5.1896</v>
       </c>
       <c r="H14" t="n">
-        <v>14.8544</v>
+        <v>-2.8302</v>
       </c>
       <c r="I14" t="n">
-        <v>7.424</v>
+        <v>-2.3594</v>
       </c>
       <c r="J14" t="n">
-        <v>17.1314</v>
+        <v>-5.0255</v>
       </c>
       <c r="K14" t="n">
-        <v>12.401</v>
+        <v>-2.5314</v>
       </c>
       <c r="L14" t="n">
-        <v>4.730500000000001</v>
+        <v>-2.4941</v>
       </c>
       <c r="M14" t="n">
-        <v>5.1471</v>
+        <v>-0.1641</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4535</v>
+        <v>-0.2988</v>
       </c>
       <c r="O14" t="n">
-        <v>2.6934</v>
+        <v>0.1346</v>
       </c>
       <c r="P14" t="n">
-        <v>3.9068</v>
+        <v>0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.7438</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>14.6509</v>
+        <v>0.586</v>
       </c>
       <c r="S14" t="n">
-        <v>8.3499</v>
+        <v>0.9003</v>
       </c>
       <c r="T14" t="n">
-        <v>7.1959</v>
+        <v>0.5744</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1541</v>
+        <v>0.3259</v>
       </c>
       <c r="V14" t="n">
-        <v>5.4838</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>8.4207</v>
+        <v>1.2186</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.9367</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. DI BONAVENTURA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB. CORNELLÀ</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9899</v>
+        <v>40.01910000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3935</v>
+        <v>22.0044</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5965</v>
+        <v>18.0149</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5580000000000001</v>
+        <v>22.2786</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5610000000000001</v>
+        <v>14.8544</v>
       </c>
       <c r="I15" t="n">
-        <v>1.119</v>
+        <v>7.424100000000002</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3782</v>
+        <v>17.1314</v>
       </c>
       <c r="K15" t="n">
-        <v>0.472</v>
+        <v>12.401</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.09379999999999999</v>
+        <v>4.730600000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1798</v>
+        <v>5.1471</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.033</v>
+        <v>2.4535</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2128</v>
+        <v>2.6934</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>3.9068</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-10.7438</v>
       </c>
       <c r="R15" t="n">
-        <v>0.586</v>
+        <v>14.6509</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1541</v>
+        <v>8.3499</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0152</v>
+        <v>7.1959</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1694</v>
+        <v>1.1541</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.4838</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>8.4207</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
-      </c>
+        <v>-2.9367</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3444</v>
+        <v>1.5349</v>
       </c>
       <c r="E16" t="n">
-        <v>2.255</v>
+        <v>1.5349</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9106</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0876</v>
+        <v>1.5349</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3735</v>
+        <v>1.5349</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7141999999999999</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0615</v>
+        <v>1.5349</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4811</v>
+        <v>1.5349</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5803</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9739</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1077</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1338</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8605</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3609</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4995</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>G. DI BONAVENTURA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1811,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2175</v>
+        <v>0.9899</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.829</v>
+        <v>0.3935</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3886</v>
+        <v>0.5965</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1156</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5188</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6344</v>
+        <v>1.119</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3692</v>
+        <v>0.3782</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0028</v>
+        <v>0.472</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4848</v>
+        <v>0.1798</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.484</v>
+        <v>-1.033</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0008</v>
+        <v>1.2128</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.586</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5159</v>
+        <v>-0.1541</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2214</v>
+        <v>0.0152</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2945</v>
+        <v>-0.1694</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1796,12 +1872,17 @@
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. BORT DOMINGUEZ</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7311</v>
+        <v>-1.1906</v>
       </c>
       <c r="E18" t="n">
-        <v>0.311</v>
+        <v>0.7201</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0421</v>
+        <v>-1.9106</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5548999999999999</v>
+        <v>-0.4473</v>
       </c>
       <c r="H18" t="n">
-        <v>0.65</v>
+        <v>-1.1615</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0951</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1047</v>
+        <v>0.5266</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0642</v>
+        <v>-0.0538</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0405</v>
+        <v>0.5803</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5498</v>
+        <v>-0.9739</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4142</v>
+        <v>-1.1077</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1356</v>
+        <v>0.1338</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2628</v>
+        <v>-0.8605</v>
       </c>
       <c r="T18" t="n">
-        <v>0.183</v>
+        <v>-0.3609</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4458</v>
+        <v>-0.4995</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8279</v>
+        <v>-0.6642</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.8279</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6677</v>
+        <v>-1.2175</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5524</v>
+        <v>-0.829</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1153</v>
+        <v>-0.3886</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0942</v>
+        <v>-0.1156</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8642</v>
+        <v>0.5188</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.23</v>
+        <v>-0.6344</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0046</v>
+        <v>0.3692</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0359</v>
+        <v>1.0028</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0988</v>
+        <v>-0.4848</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8283</v>
+        <v>-0.484</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2704</v>
+        <v>-0.0008</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4265</v>
+        <v>-0.5159</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4197</v>
+        <v>-0.2214</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0068</v>
+        <v>-0.2945</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PINEÑO JIMENEZ</t>
+          <t>P. BORT DOMINGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0328</v>
+        <v>-1.7311</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0384</v>
+        <v>0.311</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9944</v>
+        <v>-2.0421</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6406</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8716</v>
+        <v>0.65</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.769</v>
+        <v>-0.0951</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6119</v>
+        <v>1.1047</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0217</v>
+        <v>1.0642</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0287</v>
+        <v>-0.5498</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8933</v>
+        <v>-0.4142</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1354</v>
+        <v>-0.1356</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3921</v>
+        <v>-0.2628</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4497</v>
+        <v>0.183</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9424</v>
+        <v>-0.4458</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. DIAZ KAUFFMANN</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1242</v>
+        <v>-2.6677</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0429</v>
+        <v>-0.5524</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1671</v>
+        <v>-2.1153</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2223</v>
+        <v>-1.0942</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3564</v>
+        <v>-0.8642</v>
       </c>
       <c r="I21" t="n">
-        <v>0.134</v>
+        <v>-0.23</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2906</v>
+        <v>0.0046</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2906</v>
+        <v>-0.0359</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5129</v>
+        <v>-1.0988</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.647</v>
+        <v>-0.8283</v>
       </c>
       <c r="O21" t="n">
-        <v>0.134</v>
+        <v>-0.2704</v>
       </c>
       <c r="P21" t="n">
         <v>-0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2339</v>
+        <v>0.4265</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0964</v>
+        <v>0.4197</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.3304</v>
+        <v>0.0068</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>J. PINENO JIMENEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.352</v>
+        <v>-3.0328</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3787</v>
+        <v>-2.0384</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9733</v>
+        <v>-0.9944</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2764</v>
+        <v>-1.6406</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3881</v>
+        <v>-0.8716</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8883</v>
+        <v>-0.769</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8381</v>
+        <v>-0.6119</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4899</v>
+        <v>0.0217</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3482</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4382</v>
+        <v>-1.0287</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8982</v>
+        <v>-0.8933</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5401</v>
+        <v>-0.1354</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1197</v>
+        <v>-1.3921</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2175</v>
+        <v>-0.4497</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0978</v>
+        <v>-0.9424</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>P. DIAZ KAUFFMANN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2309,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1449</v>
+        <v>-3.1242</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.779</v>
+        <v>0.0429</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3659</v>
+        <v>-3.1671</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.437</v>
+        <v>-0.2223</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.0454</v>
+        <v>-0.3564</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3916</v>
+        <v>0.134</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2356</v>
+        <v>1.2906</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.4634</v>
+        <v>1.2906</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2278</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.2014</v>
+        <v>-1.5129</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.582</v>
+        <v>-1.647</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6194</v>
+        <v>0.134</v>
       </c>
       <c r="P23" t="n">
         <v>-0.7814</v>
@@ -2248,28 +2354,33 @@
         <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2587</v>
+        <v>-1.2339</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.59</v>
+        <v>0.0964</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6687</v>
+        <v>-1.3304</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3321</v>
+        <v>-0.8865</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3321</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9101</v>
+        <v>-3.352</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7425</v>
+        <v>-1.3787</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1677</v>
+        <v>-1.9733</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.917</v>
+        <v>-3.2764</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.6219</v>
+        <v>-1.3881</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2951</v>
+        <v>-1.8883</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.4784</v>
+        <v>-1.8381</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.8586</v>
+        <v>-0.4899</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6198</v>
+        <v>-1.3482</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4386</v>
+        <v>-1.4382</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7634</v>
+        <v>-0.8982</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6753</v>
+        <v>-0.5401</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1953</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9698</v>
+        <v>0.1197</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2874</v>
+        <v>0.2175</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6824</v>
+        <v>-0.0978</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X24" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.7495</v>
+        <v>-5.1449</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.6516</v>
+        <v>-2.779</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0978</v>
+        <v>-2.3659</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.3987</v>
+        <v>-3.437</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.8494</v>
+        <v>-3.0454</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.5493</v>
+        <v>-0.3916</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.272</v>
+        <v>-0.2356</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.6117</v>
+        <v>-1.4634</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6603</v>
+        <v>1.2278</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.1267</v>
+        <v>-3.2014</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.2377</v>
+        <v>-1.582</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.8891</v>
+        <v>-1.6194</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.7581</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R25" t="n">
         <v>1.1721</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1471</v>
+        <v>-1.2587</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.004</v>
+        <v>-0.59</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1432</v>
+        <v>-0.6687</v>
       </c>
       <c r="V25" t="n">
-        <v>0.5545</v>
+        <v>0.3321</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P. BERMEJO JARAMILLO</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2558,78 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.4469</v>
+        <v>-5.9101</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.0458</v>
+        <v>-3.7425</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.4011</v>
+        <v>-2.1677</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.3772</v>
+        <v>-3.917</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.8389</v>
+        <v>-2.6219</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.5383</v>
+        <v>-1.2951</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.9199</v>
+        <v>-2.4784</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.3267</v>
+        <v>-1.8586</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6198</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.4573</v>
+        <v>-1.4386</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.5121</v>
+        <v>-0.7634</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-0.6753</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1246</v>
+        <v>-0.9698</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1725</v>
+        <v>-0.2874</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9520999999999999</v>
+        <v>-0.6824</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,68 +2641,235 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-39.0424</v>
+        <v>-6.7495</v>
       </c>
       <c r="E27" t="n">
+        <v>-4.6516</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-2.0978</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-5.3987</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-2.8494</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-2.5493</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-2.272</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.6117</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.6603</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-3.1267</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1.2377</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.8891</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.1471</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.1432</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P. BERMEJO JARAMILLO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-7.4469</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-5.0458</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-2.4011</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-5.3772</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-3.8389</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-1.5383</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-2.9199</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-2.3267</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-0.5931999999999999</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-2.4573</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1.5121</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.9451000000000001</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-1.1246</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.1725</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.9520999999999999</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484337_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-39.0425</v>
+      </c>
+      <c r="E29" t="n">
         <v>-18.015</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F29" t="n">
         <v>-21.0274</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G29" t="n">
         <v>-22.2785</v>
       </c>
-      <c r="H27" t="n">
-        <v>-14.8546</v>
-      </c>
-      <c r="I27" t="n">
+      <c r="H29" t="n">
+        <v>-14.8547</v>
+      </c>
+      <c r="I29" t="n">
         <v>-7.4239</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J29" t="n">
         <v>-5.1471</v>
       </c>
-      <c r="K27" t="n">
-        <v>-2.4538</v>
-      </c>
-      <c r="L27" t="n">
+      <c r="K29" t="n">
+        <v>-2.453800000000001</v>
+      </c>
+      <c r="L29" t="n">
         <v>-2.6934</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M29" t="n">
         <v>-17.1313</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N29" t="n">
         <v>-12.4009</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O29" t="n">
         <v>-4.7306</v>
       </c>
-      <c r="P27" t="n">
-        <v>-3.9069</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="P29" t="n">
+        <v>-3.906899999999999</v>
+      </c>
+      <c r="Q29" t="n">
         <v>-14.6505</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R29" t="n">
         <v>10.744</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S29" t="n">
         <v>-7.3733</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T29" t="n">
         <v>-1.1541</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U29" t="n">
         <v>-6.2194</v>
       </c>
-      <c r="V27" t="n">
+      <c r="V29" t="n">
         <v>-5.483700000000001</v>
       </c>
-      <c r="W27" t="n">
+      <c r="W29" t="n">
         <v>2.9369</v>
       </c>
-      <c r="X27" t="n">
+      <c r="X29" t="n">
         <v>-8.4206</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
